--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487156_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487156_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7755</v>
+        <v>5.4234</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7483</v>
+        <v>2.8875</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0273</v>
+        <v>2.5359</v>
       </c>
       <c r="G2" t="n">
         <v>1.8395</v>
@@ -610,13 +610,13 @@
         <v>3.2811</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.9638</v>
+        <v>-0.3159</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9095</v>
+        <v>0.2297</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0543</v>
+        <v>-0.5457</v>
       </c>
       <c r="V2" t="n">
         <v>2.7418</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0582</v>
+        <v>1.897</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0505</v>
+        <v>0.8893</v>
       </c>
       <c r="F3" t="n">
         <v>1.0077</v>
@@ -688,10 +688,10 @@
         <v>1.3511</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.505</v>
+        <v>0.3338</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5354</v>
+        <v>0.3034</v>
       </c>
       <c r="U3" t="n">
         <v>0.0304</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7923</v>
+        <v>1.4715</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.4093</v>
+        <v>-0.9711</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2016</v>
+        <v>2.4425</v>
       </c>
       <c r="G4" t="n">
         <v>-0.6586</v>
@@ -766,13 +766,13 @@
         <v>3.0881</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4792</v>
+        <v>0.2</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1745</v>
+        <v>0.6128</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-0.4128</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. HERRERO SANDOVAL</t>
+          <t>D. BARROSO VALVERDE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4082</v>
+        <v>0.6973</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.238</v>
+        <v>0.9922</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6461</v>
+        <v>-0.2949</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0816</v>
+        <v>1.4434</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.414</v>
+        <v>-0.3974</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6676</v>
+        <v>1.8408</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6676</v>
+        <v>2.8248</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.4242</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6676</v>
+        <v>2.4006</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.414</v>
+        <v>-1.3814</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.414</v>
+        <v>-0.8216</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.5598</v>
       </c>
       <c r="P5" t="n">
         <v>0.386</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>0.386</v>
+        <v>2.3161</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4475</v>
+        <v>0.3817</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4297</v>
+        <v>0.0975</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0178</v>
+        <v>0.2842</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6562</v>
+        <v>-1.5138</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6562</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>C. HERRERO SANDOVAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0852</v>
+        <v>0.194</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.8045</v>
+        <v>-0.4789</v>
       </c>
       <c r="F6" t="n">
-        <v>4.7193</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-5.2683</v>
+        <v>-1.0816</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.1173</v>
+        <v>-0.414</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.151</v>
+        <v>-0.6676</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.7545</v>
+        <v>-0.6676</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.6228</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1317</v>
+        <v>-0.6676</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5138</v>
+        <v>-0.414</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4945</v>
+        <v>-0.414</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0193</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.386</v>
+        <v>0.386</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5091</v>
+        <v>0.386</v>
       </c>
       <c r="S6" t="n">
-        <v>3.0709</v>
+        <v>0.2333</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3313</v>
+        <v>0.1887</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7397</v>
+        <v>0.0446</v>
       </c>
       <c r="V6" t="n">
-        <v>2.4982</v>
+        <v>0.6562</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.9843</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6724</v>
+        <v>-0.839</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8328</v>
+        <v>-1.1332</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1604</v>
+        <v>0.2942</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3003</v>
@@ -1000,13 +1000,13 @@
         <v>0.579</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0139</v>
+        <v>-0.1527</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1322</v>
+        <v>-0.1682</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1183</v>
+        <v>0.0155</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. BARROSO VALVERDE</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7037</v>
+        <v>-2.0315</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-5.7871</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6162</v>
+        <v>3.7556</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4434</v>
+        <v>-5.2683</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3974</v>
+        <v>-4.1173</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8408</v>
+        <v>-1.151</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8248</v>
+        <v>-4.7545</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4242</v>
+        <v>-3.6228</v>
       </c>
       <c r="L8" t="n">
-        <v>2.4006</v>
+        <v>-1.1317</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3814</v>
+        <v>-0.5138</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8216</v>
+        <v>-0.4945</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5598</v>
+        <v>-0.0193</v>
       </c>
       <c r="P8" t="n">
-        <v>0.386</v>
+        <v>-0.386</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3161</v>
+        <v>2.5091</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0192</v>
+        <v>1.1247</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9822</v>
+        <v>0.3487</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.037</v>
+        <v>0.776</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.5138</v>
+        <v>2.4982</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5138</v>
+        <v>0.9843</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8503</v>
+        <v>-3.9177</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5724</v>
+        <v>-3.3721</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2779</v>
+        <v>-0.5456</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0535</v>
@@ -1156,13 +1156,13 @@
         <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8897</v>
+        <v>-0.9571</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6544</v>
+        <v>-0.4541</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2353</v>
+        <v>-0.503</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9421</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. DINIS</t>
+          <t>M. DIEYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4737</v>
+        <v>-4.1853</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.0809</v>
+        <v>-1.5205</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6072</v>
+        <v>-2.6648</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.0503</v>
+        <v>-0.9472</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.7086</v>
+        <v>-0.4688</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3416</v>
+        <v>-0.4784</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.8116</v>
+        <v>-0.4206</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.9552</v>
+        <v>-0.502</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8564</v>
+        <v>0.0814</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7614</v>
+        <v>-0.5266</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2466</v>
+        <v>0.0332</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5148</v>
+        <v>-0.5598</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.193</v>
+        <v>0.772</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0881</v>
+        <v>-1.158</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8951</v>
+        <v>1.9301</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1833</v>
+        <v>-0.3262</v>
       </c>
       <c r="T10" t="n">
-        <v>2.533</v>
+        <v>0.0582</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3497</v>
+        <v>-0.3844</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4137</v>
+        <v>-3.6839</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.6996</v>
+        <v>-3.6839</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. DIEYE</t>
+          <t>A. DINIS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.797</v>
+        <v>-5.7706</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.159</v>
+        <v>-6.4046</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.638</v>
+        <v>0.634</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9472</v>
+        <v>-4.0503</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4688</v>
+        <v>-2.7086</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4784</v>
+        <v>-1.3416</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4206</v>
+        <v>-4.8116</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.502</v>
+        <v>-2.9552</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0814</v>
+        <v>-1.8564</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5266</v>
+        <v>0.7614</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0332</v>
+        <v>0.2466</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5598</v>
+        <v>0.5148</v>
       </c>
       <c r="P11" t="n">
-        <v>0.772</v>
+        <v>-0.193</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.158</v>
+        <v>-3.0881</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9301</v>
+        <v>2.8951</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9379</v>
+        <v>0.8864</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5803</v>
+        <v>1.2093</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3576</v>
+        <v>-0.3229</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.6839</v>
+        <v>-2.4137</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.6839</v>
+        <v>-2.6996</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.5481</v>
+        <v>-7.060899999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>-16.3856</v>
+        <v>-14.8985</v>
       </c>
       <c r="F12" t="n">
         <v>7.8375</v>
@@ -1366,7 +1366,7 @@
         <v>-8.7509</v>
       </c>
       <c r="K12" t="n">
-        <v>-6.2734</v>
+        <v>-6.273399999999999</v>
       </c>
       <c r="L12" t="n">
         <v>-2.4775</v>
@@ -1378,7 +1378,7 @@
         <v>-1.5719</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1606999999999999</v>
+        <v>-0.1606999999999998</v>
       </c>
       <c r="P12" t="n">
         <v>1.9301</v>
@@ -1390,13 +1390,13 @@
         <v>19.3007</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.07919999999999972</v>
+        <v>1.408</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9388999999999998</v>
+        <v>2.426</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.018</v>
+        <v>-1.0181</v>
       </c>
       <c r="V12" t="n">
         <v>0.08450000000000024</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.632</v>
+        <v>6.5676</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1854</v>
+        <v>2.5859</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4466</v>
+        <v>3.9817</v>
       </c>
       <c r="G13" t="n">
         <v>5.7219</v>
@@ -1468,13 +1468,13 @@
         <v>3.0881</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7568</v>
+        <v>0.1788</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2842</v>
+        <v>0.1164</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4726</v>
+        <v>0.0624</v>
       </c>
       <c r="V13" t="n">
         <v>-0.4912</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.249</v>
+        <v>2.9096</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6292</v>
+        <v>-0.1285</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8781</v>
+        <v>3.0381</v>
       </c>
       <c r="G14" t="n">
         <v>-1.5234</v>
@@ -1546,13 +1546,13 @@
         <v>1.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4502</v>
+        <v>-0.7896</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1157</v>
+        <v>-0.615</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3345</v>
+        <v>-0.1745</v>
       </c>
       <c r="V14" t="n">
         <v>4.2576</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. MARTINEZ FERNANDEZ</t>
+          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2192</v>
+        <v>2.3935</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.7516</v>
+        <v>1.8618</v>
       </c>
       <c r="F15" t="n">
-        <v>4.9708</v>
+        <v>0.5317</v>
       </c>
       <c r="G15" t="n">
-        <v>0.461</v>
+        <v>4.0665</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3437</v>
+        <v>2.3836</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8047</v>
+        <v>1.683</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.4624</v>
+        <v>2.3501</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.6252</v>
+        <v>1.3091</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1628</v>
+        <v>1.0411</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9234</v>
+        <v>1.7164</v>
       </c>
       <c r="N15" t="n">
-        <v>1.2815</v>
+        <v>1.0745</v>
       </c>
       <c r="O15" t="n">
         <v>0.6419</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.5091</v>
+        <v>-0.579</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.8252</v>
+        <v>-2.8951</v>
       </c>
       <c r="R15" t="n">
         <v>2.3161</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4832</v>
+        <v>-0.0291</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0801</v>
+        <v>0.279</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4031</v>
+        <v>-0.3081</v>
       </c>
       <c r="V15" t="n">
-        <v>2.784</v>
+        <v>-1.0649</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4559</v>
+        <v>2.1278</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3281</v>
+        <v>-3.1927</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
+          <t>S. MARTINEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5118</v>
+        <v>1.4571</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4612</v>
+        <v>-3.3524</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0505</v>
+        <v>4.8095</v>
       </c>
       <c r="G16" t="n">
-        <v>4.0665</v>
+        <v>0.461</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3836</v>
+        <v>-0.3437</v>
       </c>
       <c r="I16" t="n">
-        <v>1.683</v>
+        <v>0.8047</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3501</v>
+        <v>-1.4624</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3091</v>
+        <v>-1.6252</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0411</v>
+        <v>0.1628</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7164</v>
+        <v>1.9234</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0745</v>
+        <v>1.2815</v>
       </c>
       <c r="O16" t="n">
         <v>0.6419</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.579</v>
+        <v>-2.5091</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8951</v>
+        <v>-4.8252</v>
       </c>
       <c r="R16" t="n">
         <v>2.3161</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9108000000000001</v>
+        <v>0.7211</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1216</v>
+        <v>0.4793</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7893</v>
+        <v>0.2419</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0649</v>
+        <v>2.784</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1278</v>
+        <v>2.4559</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.1927</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. QUINCY-JONES</t>
+          <t>M. CARCOBA BEDIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4872</v>
+        <v>1.412</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.4325</v>
+        <v>-0.6231</v>
       </c>
       <c r="F17" t="n">
-        <v>3.9197</v>
+        <v>2.0351</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2049</v>
+        <v>1.6249</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7043</v>
+        <v>2.2025</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.4994</v>
+        <v>-0.5777</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6703</v>
+        <v>0.5825</v>
       </c>
       <c r="K17" t="n">
-        <v>2.551</v>
+        <v>1.128</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.8807</v>
+        <v>-0.5455</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5346</v>
+        <v>1.0424</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1533</v>
+        <v>1.0745</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3813</v>
+        <v>-0.0321</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3511</v>
+        <v>1.158</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.8602</v>
+        <v>-0.965</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5091</v>
+        <v>2.1231</v>
       </c>
       <c r="S17" t="n">
-        <v>2.823</v>
+        <v>-0.5939</v>
       </c>
       <c r="T17" t="n">
-        <v>1.17</v>
+        <v>-0.2406</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6531</v>
+        <v>-0.3533</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.1897</v>
+        <v>-0.7771</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.4126</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>-0.7771</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. CARCOBA BEDIA</t>
+          <t>A. QUINCY-JONES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5828</v>
+        <v>-0.0506</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6231</v>
+        <v>-3.0333</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2059</v>
+        <v>2.9828</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6249</v>
+        <v>1.2049</v>
       </c>
       <c r="H18" t="n">
-        <v>2.2025</v>
+        <v>2.7043</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5777</v>
+        <v>-1.4994</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5825</v>
+        <v>0.6703</v>
       </c>
       <c r="K18" t="n">
-        <v>1.128</v>
+        <v>2.551</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5455</v>
+        <v>-1.8807</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0424</v>
+        <v>0.5346</v>
       </c>
       <c r="N18" t="n">
-        <v>1.0745</v>
+        <v>0.1533</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0321</v>
+        <v>0.3813</v>
       </c>
       <c r="P18" t="n">
-        <v>1.158</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.965</v>
+        <v>-3.8602</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1231</v>
+        <v>2.5091</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4231</v>
+        <v>1.2853</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2406</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1825</v>
+        <v>0.7161</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7771</v>
+        <v>-1.1897</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.4126</v>
       </c>
       <c r="X18" t="n">
         <v>-0.7771</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8512</v>
+        <v>-0.9583</v>
       </c>
       <c r="E19" t="n">
         <v>-1.0038</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1526</v>
+        <v>0.0455</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0528</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1666</v>
+        <v>0.0595</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2261</v>
+        <v>0.119</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8358</v>
+        <v>-1.0872</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4041</v>
+        <v>-2.0035</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5683</v>
+        <v>0.9163</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0063</v>
@@ -2014,13 +2014,13 @@
         <v>1.9301</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1104</v>
+        <v>0.6382</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0132</v>
+        <v>0.4138</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1236</v>
+        <v>0.2244</v>
       </c>
       <c r="V20" t="n">
         <v>-1.7192</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4466</v>
+        <v>-2.7603</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6398</v>
+        <v>-2.1405</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8069</v>
+        <v>-0.6198</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0132</v>
@@ -2092,13 +2092,13 @@
         <v>1.158</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2578</v>
+        <v>-0.0559</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5764</v>
+        <v>0.0757</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3186</v>
+        <v>-0.1316</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8842</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>8.548400000000001</v>
+        <v>9.883399999999998</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.837499999999999</v>
+        <v>-7.837400000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>16.3856</v>
+        <v>17.7209</v>
       </c>
       <c r="G22" t="n">
         <v>10.4835</v>
@@ -2170,13 +2170,13 @@
         <v>17.3707</v>
       </c>
       <c r="S22" t="n">
-        <v>0.07930000000000009</v>
+        <v>1.4144</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0181</v>
+        <v>1.0182</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9388000000000001</v>
+        <v>0.3963</v>
       </c>
       <c r="V22" t="n">
         <v>-0.0847</v>
